--- a/results/10-2025/beta/without_shutdown_deflators/differences.xlsx
+++ b/results/10-2025/beta/without_shutdown_deflators/differences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CParry\Downloads\FIM\results\10-2025\beta\without_shutdown_deflators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBFE8E15-4061-4A0A-A593-05A704AC4EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8509CAD2-AD86-43A9-82BE-EB822D972727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28995" yWindow="-11505" windowWidth="9195" windowHeight="8175" xr2:uid="{0E707EDA-3955-4EBD-8922-EBBD29D8FDA3}"/>
+    <workbookView xWindow="14985" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0E707EDA-3955-4EBD-8922-EBBD29D8FDA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Shutdown Effects" sheetId="1" r:id="rId1"/>
-    <sheet name="tariff effects" sheetId="2" r:id="rId2"/>
-    <sheet name="OBBBA effects" sheetId="3" r:id="rId3"/>
+    <sheet name="Tariff Effects" sheetId="2" r:id="rId2"/>
+    <sheet name="OBBBA Effects" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>plus 10% in q4 -8.4% in q1</t>
   </si>
@@ -116,13 +116,70 @@
   </si>
   <si>
     <t>federal_non_corporate_taxes_contribution</t>
+  </si>
+  <si>
+    <t>Federal Noncorporate Taxes</t>
+  </si>
+  <si>
+    <t>Federal Corporate Taxes</t>
+  </si>
+  <si>
+    <t>Student Loans</t>
+  </si>
+  <si>
+    <t>Federal Purchases</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Transfers</t>
+  </si>
+  <si>
+    <t>federal_non_corporate_taxes</t>
+  </si>
+  <si>
+    <t>With OBBBA</t>
+  </si>
+  <si>
+    <t>Without OBBBA</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>federal_corporate_taxes</t>
+  </si>
+  <si>
+    <t>federal_student_loans</t>
+  </si>
+  <si>
+    <t>federal_purchases</t>
+  </si>
+  <si>
+    <t>federal_social_benefits</t>
+  </si>
+  <si>
+    <t>Social Benefits</t>
+  </si>
+  <si>
+    <t>federal_health_outlays</t>
+  </si>
+  <si>
+    <t>Medicaid</t>
+  </si>
+  <si>
+    <t>state_health_outlays</t>
+  </si>
+  <si>
+    <t>Total Effect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -130,13 +187,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -151,10 +225,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,7 +587,7 @@
         <v>-0.14802611157274501</v>
       </c>
       <c r="D2">
-        <f>B2-C2</f>
+        <f t="shared" ref="D2:D18" si="0">B2-C2</f>
         <v>0</v>
       </c>
     </row>
@@ -498,7 +602,7 @@
         <v>0.29138772747964098</v>
       </c>
       <c r="D3">
-        <f>B3-C3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -513,7 +617,7 @@
         <v>7.0409518749265695E-2</v>
       </c>
       <c r="D4">
-        <f>B4-C4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -528,7 +632,7 @@
         <v>-9.5656904722252106E-2</v>
       </c>
       <c r="D5">
-        <f>B5-C5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -543,7 +647,7 @@
         <v>0.12347864355657601</v>
       </c>
       <c r="D6">
-        <f>B6-C6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -558,7 +662,7 @@
         <v>0.40650570357638799</v>
       </c>
       <c r="D7">
-        <f>B7-C7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -573,7 +677,7 @@
         <v>0.133873781721287</v>
       </c>
       <c r="D8">
-        <f>B8-C8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -588,7 +692,7 @@
         <v>-0.51945344220673595</v>
       </c>
       <c r="D9">
-        <f>B9-C9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -603,7 +707,7 @@
         <v>-0.49659070787292697</v>
       </c>
       <c r="D10">
-        <f>B10-C10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -618,7 +722,7 @@
         <v>0.163111297253933</v>
       </c>
       <c r="D11">
-        <f>B11-C11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -633,7 +737,7 @@
         <v>5.1277427045617302E-2</v>
       </c>
       <c r="D12">
-        <f>B12-C12</f>
+        <f t="shared" si="0"/>
         <v>-0.60217146393573928</v>
       </c>
     </row>
@@ -648,7 +752,7 @@
         <v>0.29588504945161798</v>
       </c>
       <c r="D13">
-        <f>B13-C13</f>
+        <f t="shared" si="0"/>
         <v>0.59764743927240005</v>
       </c>
     </row>
@@ -663,7 +767,7 @@
         <v>2.5063031368209299E-2</v>
       </c>
       <c r="D14">
-        <f>B14-C14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -678,7 +782,7 @@
         <v>-3.9419277329213298E-2</v>
       </c>
       <c r="D15">
-        <f>B15-C15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -693,7 +797,7 @@
         <v>-0.134754265364598</v>
       </c>
       <c r="D16">
-        <f>B16-C16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -708,7 +812,7 @@
         <v>-6.4067477393471503E-2</v>
       </c>
       <c r="D17">
-        <f>B17-C17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -723,7 +827,7 @@
         <v>-0.110727166879507</v>
       </c>
       <c r="D18">
-        <f>B18-C18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -751,7 +855,7 @@
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -772,7 +876,7 @@
         <v>0.40168306970290102</v>
       </c>
       <c r="D2">
-        <f>C2-B2</f>
+        <f>B2-C2</f>
         <v>0</v>
       </c>
     </row>
@@ -787,7 +891,7 @@
         <v>0.113357457258702</v>
       </c>
       <c r="D3">
-        <f>C3-B3</f>
+        <f t="shared" ref="D3:D18" si="0">B3-C3</f>
         <v>0</v>
       </c>
     </row>
@@ -802,7 +906,7 @@
         <v>8.4390722113830099E-2</v>
       </c>
       <c r="D4">
-        <f>C4-B4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -817,7 +921,7 @@
         <v>0.49002857232950098</v>
       </c>
       <c r="D5">
-        <f>C5-B5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -832,7 +936,7 @@
         <v>0.350634639232693</v>
       </c>
       <c r="D6">
-        <f>C6-B6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -847,7 +951,7 @@
         <v>0.26769889286291498</v>
       </c>
       <c r="D7">
-        <f>C7-B7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -862,7 +966,7 @@
         <v>0.26578106401662999</v>
       </c>
       <c r="D8">
-        <f>C8-B8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -877,7 +981,7 @@
         <v>-6.8923507981179702E-2</v>
       </c>
       <c r="D9">
-        <f>C9-B9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -889,11 +993,11 @@
         <v>-0.49360351627841198</v>
       </c>
       <c r="C10">
-        <v>-0.49360351627841198</v>
+        <v>-0.21567094977110701</v>
       </c>
       <c r="D10">
-        <f>C10-B10</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-0.27793256650730497</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -904,11 +1008,11 @@
         <v>-0.225617648258191</v>
       </c>
       <c r="C11">
-        <v>0.18591672941149001</v>
+        <v>0.183825060946469</v>
       </c>
       <c r="D11">
-        <f>B11-C11</f>
-        <v>-0.41153437766968104</v>
+        <f t="shared" si="0"/>
+        <v>-0.40944270920465997</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -919,11 +1023,11 @@
         <v>-0.18376482299076699</v>
       </c>
       <c r="C12">
-        <v>0.30922527074513401</v>
+        <v>0.17518373666777601</v>
       </c>
       <c r="D12">
-        <f>B12-C12</f>
-        <v>-0.49299009373590097</v>
+        <f t="shared" si="0"/>
+        <v>-0.358948559658543</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -934,11 +1038,11 @@
         <v>-0.157889086807043</v>
       </c>
       <c r="C13">
-        <v>0.124777734619577</v>
+        <v>0.12718876709139601</v>
       </c>
       <c r="D13">
-        <f>B13-C13</f>
-        <v>-0.28266682142662003</v>
+        <f t="shared" si="0"/>
+        <v>-0.28507785389843898</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -949,11 +1053,11 @@
         <v>-0.108594546287687</v>
       </c>
       <c r="C14">
-        <v>0.12555896919251699</v>
+        <v>0.128735948590391</v>
       </c>
       <c r="D14">
-        <f>B14-C14</f>
-        <v>-0.23415351548020399</v>
+        <f t="shared" si="0"/>
+        <v>-0.237330494878078</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -964,11 +1068,11 @@
         <v>-0.107081655066805</v>
       </c>
       <c r="C15">
-        <v>0.122217372481947</v>
+        <v>0.126084682237845</v>
       </c>
       <c r="D15">
-        <f>B15-C15</f>
-        <v>-0.229299027548752</v>
+        <f t="shared" si="0"/>
+        <v>-0.23316633730465</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -979,11 +1083,11 @@
         <v>-8.53676104400794E-2</v>
       </c>
       <c r="C16">
-        <v>0.14063965098947201</v>
+        <v>0.14519450482926699</v>
       </c>
       <c r="D16">
-        <f>B16-C16</f>
-        <v>-0.22600726142955141</v>
+        <f t="shared" si="0"/>
+        <v>-0.23056211526934639</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -994,11 +1098,11 @@
         <v>-0.194568075207978</v>
       </c>
       <c r="C17">
-        <v>2.87695140232813E-2</v>
+        <v>3.4041001179858997E-2</v>
       </c>
       <c r="D17">
-        <f>B17-C17</f>
-        <v>-0.22333758923125929</v>
+        <f t="shared" si="0"/>
+        <v>-0.22860907638783701</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1009,11 +1113,11 @@
         <v>-2.9836760326829598E-2</v>
       </c>
       <c r="C18">
-        <v>0.18881224837854199</v>
+        <v>6.8448435027690602E-2</v>
       </c>
       <c r="D18">
-        <f>B18-C18</f>
-        <v>-0.2186490087053716</v>
+        <f t="shared" si="0"/>
+        <v>-9.8285195354520197E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1023,225 +1127,1782 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE93320E-ECC3-44F5-BE40-582080B7A03B}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" customWidth="1"/>
+    <col min="11" max="11" width="16.54296875" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
+    <col min="15" max="15" width="15.7265625" customWidth="1"/>
+    <col min="16" max="16" width="13.08984375" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" customWidth="1"/>
+    <col min="20" max="20" width="14.6328125" customWidth="1"/>
+    <col min="31" max="31" width="13.90625" customWidth="1"/>
+    <col min="35" max="35" width="12.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="C1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="G1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="K1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="O1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="S1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="W1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="AA1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="S2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="W2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+    </row>
+    <row r="3" spans="1:35" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI3" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B2">
+      <c r="C4" s="5">
         <v>0.40168306970290102</v>
       </c>
-      <c r="C2">
+      <c r="D4" s="5">
         <v>0.40168306970290102</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="E4" s="5">
+        <f>C4-D4</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>-8.21940867312759E-2</v>
+      </c>
+      <c r="H4">
+        <v>-8.21940867312759E-2</v>
+      </c>
+      <c r="I4" s="5">
+        <f>G4-H4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4">
+        <v>-8.0992848567109695E-3</v>
+      </c>
+      <c r="L4">
+        <v>-8.0992848567109695E-3</v>
+      </c>
+      <c r="M4" s="5">
+        <f>K4-L4</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>-0.14802611157274501</v>
+      </c>
+      <c r="P4">
+        <v>-0.14802611157274501</v>
+      </c>
+      <c r="Q4" s="5">
+        <f>O4-P4</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>-0.110305489658881</v>
+      </c>
+      <c r="T4">
+        <v>-0.110305489658881</v>
+      </c>
+      <c r="U4" s="5">
+        <f>S4-T4</f>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.171036490137769</v>
+      </c>
+      <c r="X4">
+        <v>0.171036490137769</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>W4-X4</f>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0.10677013991119801</v>
+      </c>
+      <c r="AB4">
+        <v>0.10677013991119801</v>
+      </c>
+      <c r="AC4" s="5">
+        <f>AA4-AB4</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5">
+        <f>Q4</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <f>AC4+Y4+U4+M4</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <f>E4+I4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f>E4+I4+M4+Q4+U4+Y4+AC4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
+      <c r="C5" s="5">
         <v>0.113357457258702</v>
       </c>
-      <c r="C3">
+      <c r="D5" s="5">
         <v>0.113357457258702</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="E5" s="5">
+        <f t="shared" ref="E5:E20" si="0">C5-D5</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>-5.91532101359378E-2</v>
+      </c>
+      <c r="H5">
+        <v>-5.91532101359378E-2</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I20" si="1">G5-H5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5">
+        <v>-0.13797271237506301</v>
+      </c>
+      <c r="L5">
+        <v>-0.13797271237506301</v>
+      </c>
+      <c r="M5" s="5">
+        <f t="shared" ref="M5:M20" si="2">K5-L5</f>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0.29138772747964098</v>
+      </c>
+      <c r="P5">
+        <v>0.29138772747964098</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" ref="Q5:Q20" si="3">O5-P5</f>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>-3.5337896134434499E-2</v>
+      </c>
+      <c r="T5">
+        <v>-3.5337896134434499E-2</v>
+      </c>
+      <c r="U5" s="5">
+        <f t="shared" ref="U5:U20" si="4">S5-T5</f>
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>-8.0930364752975201E-2</v>
+      </c>
+      <c r="X5">
+        <v>-8.0930364752975201E-2</v>
+      </c>
+      <c r="Y5" s="5">
+        <f t="shared" ref="Y5:Y20" si="5">W5-X5</f>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0.246367721831767</v>
+      </c>
+      <c r="AB5">
+        <v>0.246367721831767</v>
+      </c>
+      <c r="AC5" s="5">
+        <f t="shared" ref="AC5:AC20" si="6">AA5-AB5</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5">
+        <f t="shared" ref="AE5:AE20" si="7">Q5</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="5">
+        <f t="shared" ref="AF5:AF20" si="8">AC5+Y5+U5+M5</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="5">
+        <f>E5+I5</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <f>E5+I5+M5+Q5+U5+Y5+AC5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B4">
+      <c r="C6" s="5">
         <v>8.4390722113830099E-2</v>
       </c>
-      <c r="C4">
+      <c r="D6" s="5">
         <v>8.4390722113830099E-2</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>-7.1699905905479602E-2</v>
+      </c>
+      <c r="H6">
+        <v>-7.1699905905479602E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6">
+        <v>-0.112668281418978</v>
+      </c>
+      <c r="L6">
+        <v>-0.112668281418978</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>7.0409518749265695E-2</v>
+      </c>
+      <c r="P6">
+        <v>7.0409518749265695E-2</v>
+      </c>
+      <c r="Q6" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>-0.20119765322797301</v>
+      </c>
+      <c r="T6">
+        <v>-0.20119765322797301</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>5.7480661108821697E-2</v>
+      </c>
+      <c r="X6">
+        <v>5.7480661108821697E-2</v>
+      </c>
+      <c r="Y6" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>7.3497892891865396E-2</v>
+      </c>
+      <c r="AB6">
+        <v>7.3497892891865396E-2</v>
+      </c>
+      <c r="AC6" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <f>E6+I6</f>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f>E6+I6+M6+Q6+U6+Y6+AC6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="C7" s="5">
         <v>0.49002857232950098</v>
       </c>
-      <c r="C5">
+      <c r="D7" s="5">
         <v>0.49002857232950098</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>-6.0391933673744902E-2</v>
+      </c>
+      <c r="H7">
+        <v>-6.0391933673744902E-2</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7">
+        <v>-0.104470891080262</v>
+      </c>
+      <c r="L7">
+        <v>-0.104470891080262</v>
+      </c>
+      <c r="M7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>-9.5656904722252106E-2</v>
+      </c>
+      <c r="P7">
+        <v>-9.5656904722252106E-2</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>-1.5431334318346699E-2</v>
+      </c>
+      <c r="T7">
+        <v>-1.5431334318346699E-2</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>-0.139181652755761</v>
+      </c>
+      <c r="X7">
+        <v>-0.139181652755761</v>
+      </c>
+      <c r="Y7" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0.13055531739648699</v>
+      </c>
+      <c r="AB7">
+        <v>0.13055531739648699</v>
+      </c>
+      <c r="AC7" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="5">
+        <f>E7+I7</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f>E7+I7+M7+Q7+U7+Y7+AC7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
+      <c r="C8" s="5">
         <v>0.350634639232693</v>
       </c>
-      <c r="C6">
+      <c r="D8" s="5">
         <v>0.350634639232693</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>-4.6919376760871503E-2</v>
+      </c>
+      <c r="H8">
+        <v>-4.6919376760871503E-2</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8">
+        <v>-9.6103418388998496E-2</v>
+      </c>
+      <c r="L8">
+        <v>-9.6103418388998496E-2</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0.12347864355657601</v>
+      </c>
+      <c r="P8">
+        <v>0.12347864355657601</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.17944505351008599</v>
+      </c>
+      <c r="T8">
+        <v>0.17944505351008599</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>-0.10798661114378599</v>
+      </c>
+      <c r="X8">
+        <v>-0.10798661114378599</v>
+      </c>
+      <c r="Y8" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0.112651604454477</v>
+      </c>
+      <c r="AB8">
+        <v>0.112651604454477</v>
+      </c>
+      <c r="AC8" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <f>E8+I8</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <f>E8+I8+M8+Q8+U8+Y8+AC8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="C9" s="5">
         <v>0.26769889286291498</v>
       </c>
-      <c r="C7">
+      <c r="D9" s="5">
         <v>0.26769889286291498</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>-4.3703023830997202E-2</v>
+      </c>
+      <c r="H9">
+        <v>-4.3703023830997202E-2</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9">
+        <v>-5.5729672642463098E-2</v>
+      </c>
+      <c r="L9">
+        <v>-5.5729672642463098E-2</v>
+      </c>
+      <c r="M9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0.40650570357638799</v>
+      </c>
+      <c r="P9">
+        <v>0.40650570357638799</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0.262851861848517</v>
+      </c>
+      <c r="T9">
+        <v>0.262851861848517</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.20674711777249699</v>
+      </c>
+      <c r="X9">
+        <v>0.20674711777249699</v>
+      </c>
+      <c r="Y9" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>4.4619556639790899E-2</v>
+      </c>
+      <c r="AB9">
+        <v>4.4619556639790899E-2</v>
+      </c>
+      <c r="AC9" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <f>E9+I9</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="4">
+        <f>E9+I9+M9+Q9+U9+Y9+AC9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="C10" s="5">
         <v>0.26578106401662999</v>
       </c>
-      <c r="C8">
+      <c r="D10" s="5">
         <v>0.26578106401662999</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>-3.4339266354473298E-2</v>
+      </c>
+      <c r="H10">
+        <v>-3.4339266354473298E-2</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10">
+        <v>-3.0672088360098701E-2</v>
+      </c>
+      <c r="L10">
+        <v>-3.0672088360098701E-2</v>
+      </c>
+      <c r="M10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0.133873781721287</v>
+      </c>
+      <c r="P10">
+        <v>0.133873781721287</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0.27225397073088298</v>
+      </c>
+      <c r="T10">
+        <v>0.27225397073088298</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.14998115565769099</v>
+      </c>
+      <c r="X10">
+        <v>0.14998115565769099</v>
+      </c>
+      <c r="Y10" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0.15091666254341701</v>
+      </c>
+      <c r="AB10">
+        <v>0.15091666254341701</v>
+      </c>
+      <c r="AC10" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <f>E10+I10</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="4">
+        <f>E10+I10+M10+Q10+U10+Y10+AC10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="C11" s="5">
         <v>-6.8923507981179702E-2</v>
       </c>
-      <c r="C9">
+      <c r="D11" s="5">
         <v>-6.8923507981179702E-2</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>-4.2648201337320401E-3</v>
+      </c>
+      <c r="H11">
+        <v>-4.2648201337320401E-3</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11">
+        <v>-3.0099482833375799E-2</v>
+      </c>
+      <c r="L11">
+        <v>-3.0099482833375799E-2</v>
+      </c>
+      <c r="M11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>-0.51945344220673595</v>
+      </c>
+      <c r="P11">
+        <v>-0.51945344220673595</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0.18178302235421301</v>
+      </c>
+      <c r="T11">
+        <v>0.18178302235421301</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.103999770504797</v>
+      </c>
+      <c r="X11">
+        <v>0.103999770504797</v>
+      </c>
+      <c r="Y11" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>2.61260701306016E-3</v>
+      </c>
+      <c r="AB11">
+        <v>2.61260701306016E-3</v>
+      </c>
+      <c r="AC11" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <f>E11+I11</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="4">
+        <f>E11+I11+M11+Q11+U11+Y11+AC11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="C12" s="5">
         <v>-0.49360351627841198</v>
       </c>
-      <c r="C10">
+      <c r="D12" s="5">
         <v>-0.49360351627841198</v>
       </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>7.0579943690931299E-3</v>
+      </c>
+      <c r="H12">
+        <v>7.0579943690931299E-3</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12">
+        <v>-2.3738219379538301E-2</v>
+      </c>
+      <c r="L12">
+        <v>-2.3738219379538301E-2</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>-0.49659070787292697</v>
+      </c>
+      <c r="P12">
+        <v>-0.49659070787292697</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0.46724310870124203</v>
+      </c>
+      <c r="T12">
+        <v>0.46724310870124203</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.285016460293538</v>
+      </c>
+      <c r="X12">
+        <v>0.285016460293538</v>
+      </c>
+      <c r="Y12" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>-2.99527412765348E-2</v>
+      </c>
+      <c r="AB12">
+        <v>-2.99527412765348E-2</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <f>E12+I12</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="4">
+        <f>E12+I12+M12+Q12+U12+Y12+AC12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>0.18591672941149001</v>
-      </c>
-      <c r="C11">
+      <c r="C13" s="5">
         <v>-0.225617648258191</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="D13" s="5">
+        <v>-0.414381626409276</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>0.188763978151085</v>
+      </c>
+      <c r="G13">
+        <v>0.18570531800002099</v>
+      </c>
+      <c r="H13">
+        <v>5.6885468426966001E-3</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="1"/>
+        <v>0.1800167711573244</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13">
+        <v>-2.9638323362874801E-2</v>
+      </c>
+      <c r="L13">
+        <v>9.9183752678764695E-5</v>
+      </c>
+      <c r="M13" s="5">
+        <f t="shared" si="2"/>
+        <v>-2.9737507115553567E-2</v>
+      </c>
+      <c r="O13">
+        <v>1.83533240147938E-3</v>
+      </c>
+      <c r="P13">
+        <v>-0.25672407182756202</v>
+      </c>
+      <c r="Q13" s="5">
+        <f t="shared" si="3"/>
+        <v>0.25855940422904139</v>
+      </c>
+      <c r="S13">
+        <v>0.26976939094510399</v>
+      </c>
+      <c r="T13">
+        <v>0.26976939094510399</v>
+      </c>
+      <c r="U13" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.22450059422556301</v>
+      </c>
+      <c r="X13">
+        <v>0.22450059422556301</v>
+      </c>
+      <c r="Y13" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>1.9343238159436999E-3</v>
+      </c>
+      <c r="AB13">
+        <v>1.9343238159436999E-3</v>
+      </c>
+      <c r="AC13" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5">
+        <f t="shared" si="7"/>
+        <v>0.25855940422904139</v>
+      </c>
+      <c r="AF13" s="5">
+        <f t="shared" si="8"/>
+        <v>-2.9737507115553567E-2</v>
+      </c>
+      <c r="AG13" s="5">
+        <f>E13+I13</f>
+        <v>0.36878074930840943</v>
+      </c>
+      <c r="AI13" s="4">
+        <f>E13+I13+M13+Q13+U13+Y13+AC13</f>
+        <v>0.59760264642189731</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B12">
-        <v>0.30922527074513401</v>
-      </c>
-      <c r="C12">
+      <c r="C14" s="5">
         <v>-0.18376482299076699</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="D14" s="5">
+        <v>-0.36899443706361301</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.18522961407284602</v>
+      </c>
+      <c r="G14">
+        <v>6.5942042814213703E-2</v>
+      </c>
+      <c r="H14">
+        <v>4.6392729159142497E-3</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="1"/>
+        <v>6.1302769898299456E-2</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14">
+        <v>-2.4548492152382501E-2</v>
+      </c>
+      <c r="L14">
+        <v>8.8049722765629596E-5</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="2"/>
+        <v>-2.4636541875148129E-2</v>
+      </c>
+      <c r="O14">
+        <v>-0.40818665265298099</v>
+      </c>
+      <c r="P14">
+        <v>-0.53890896042332004</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="3"/>
+        <v>0.13072230777033905</v>
+      </c>
+      <c r="S14">
+        <v>0.21821118449858201</v>
+      </c>
+      <c r="T14">
+        <v>0.24209083473686599</v>
+      </c>
+      <c r="U14" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.3879650238283978E-2</v>
+      </c>
+      <c r="W14">
+        <v>0.22947080428754399</v>
+      </c>
+      <c r="X14">
+        <v>0.22947080428754399</v>
+      </c>
+      <c r="Y14" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>2.0152617978004699E-2</v>
+      </c>
+      <c r="AB14">
+        <v>2.0152617978004699E-2</v>
+      </c>
+      <c r="AC14" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5">
+        <f t="shared" si="7"/>
+        <v>0.13072230777033905</v>
+      </c>
+      <c r="AF14" s="5">
+        <f t="shared" si="8"/>
+        <v>-4.8516192113432111E-2</v>
+      </c>
+      <c r="AG14" s="5">
+        <f>E14+I14</f>
+        <v>0.24653238397114546</v>
+      </c>
+      <c r="AI14" s="4">
+        <f>E14+I14+M14+Q14+U14+Y14+AC14</f>
+        <v>0.32873849962805241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B13">
-        <v>0.124777734619577</v>
-      </c>
-      <c r="C13">
+      <c r="C15" s="5">
         <v>-0.157889086807043</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="D15" s="5">
+        <v>-0.66605164662537797</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.50816255981833502</v>
+      </c>
+      <c r="G15">
+        <v>6.3538307727449006E-2</v>
+      </c>
+      <c r="H15">
+        <v>3.9148396399947801E-3</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="1"/>
+        <v>5.9623468087454223E-2</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15">
+        <v>-2.2803875892856401E-2</v>
+      </c>
+      <c r="L15">
+        <v>-1.7145974559277E-4</v>
+      </c>
+      <c r="M15" s="5">
+        <f t="shared" si="2"/>
+        <v>-2.2632416147263631E-2</v>
+      </c>
+      <c r="O15">
+        <v>0.89353248872401803</v>
+      </c>
+      <c r="P15">
+        <v>0.67078724466986295</v>
+      </c>
+      <c r="Q15" s="5">
+        <f t="shared" si="3"/>
+        <v>0.22274524405415508</v>
+      </c>
+      <c r="S15">
+        <v>0.150319148575252</v>
+      </c>
+      <c r="T15">
+        <v>0.17365917817197701</v>
+      </c>
+      <c r="U15" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.3340029596725015E-2</v>
+      </c>
+      <c r="W15">
+        <v>0.27300490883686801</v>
+      </c>
+      <c r="X15">
+        <v>0.27300490883686801</v>
+      </c>
+      <c r="Y15" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>2.93317054991943E-2</v>
+      </c>
+      <c r="AB15">
+        <v>2.93317054991943E-2</v>
+      </c>
+      <c r="AC15" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5">
+        <f t="shared" si="7"/>
+        <v>0.22274524405415508</v>
+      </c>
+      <c r="AF15" s="5">
+        <f t="shared" si="8"/>
+        <v>-4.5972445743988649E-2</v>
+      </c>
+      <c r="AG15" s="5">
+        <f>E15+I15</f>
+        <v>0.56778602790578925</v>
+      </c>
+      <c r="AI15" s="4">
+        <f>E15+I15+M15+Q15+U15+Y15+AC15</f>
+        <v>0.7445588262159557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B14">
-        <v>0.12555896919251699</v>
-      </c>
-      <c r="C14">
+      <c r="C16" s="5">
         <v>-0.108594546287687</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="D16" s="5">
+        <v>-0.60953638599864701</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.50094183971095996</v>
+      </c>
+      <c r="G16">
+        <v>6.1199868765372603E-2</v>
+      </c>
+      <c r="H16">
+        <v>3.0297408438642098E-3</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="1"/>
+        <v>5.8170127921508392E-2</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16">
+        <v>-2.0976970786457501E-2</v>
+      </c>
+      <c r="L16">
+        <v>-1.99755982666422E-4</v>
+      </c>
+      <c r="M16" s="5">
+        <f t="shared" si="2"/>
+        <v>-2.0777214803791078E-2</v>
+      </c>
+      <c r="O16">
+        <v>2.5063031368209299E-2</v>
+      </c>
+      <c r="P16">
+        <v>-0.10034773664140199</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" si="3"/>
+        <v>0.12541076800961129</v>
+      </c>
+      <c r="S16">
+        <v>-5.1940570295064298E-2</v>
+      </c>
+      <c r="T16">
+        <v>-2.8984415025764598E-2</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.29561552692997E-2</v>
+      </c>
+      <c r="W16">
+        <v>0.186608335863096</v>
+      </c>
+      <c r="X16">
+        <v>0.186608335863096</v>
+      </c>
+      <c r="Y16" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>3.1639762071453803E-2</v>
+      </c>
+      <c r="AB16">
+        <v>3.1639762071453803E-2</v>
+      </c>
+      <c r="AC16" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5">
+        <f t="shared" si="7"/>
+        <v>0.12541076800961129</v>
+      </c>
+      <c r="AF16" s="5">
+        <f t="shared" si="8"/>
+        <v>-4.3733370073090777E-2</v>
+      </c>
+      <c r="AG16" s="5">
+        <f>E16+I16</f>
+        <v>0.5591119676324684</v>
+      </c>
+      <c r="AI16" s="4">
+        <f>E16+I16+M16+Q16+U16+Y16+AC16</f>
+        <v>0.6407893655689888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>5</v>
       </c>
-      <c r="B15">
-        <v>0.122217372481947</v>
-      </c>
-      <c r="C15">
+      <c r="C17" s="5">
         <v>-0.107081655066805</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="D17" s="5">
+        <v>-0.39356567686977401</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.286484021802969</v>
+      </c>
+      <c r="G17">
+        <v>6.6290283313533593E-2</v>
+      </c>
+      <c r="H17">
+        <v>9.9076530341269693E-3</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="1"/>
+        <v>5.6382630279406626E-2</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="K17">
+        <v>-1.9015005404116901E-2</v>
+      </c>
+      <c r="L17">
+        <v>-7.2697937252989599E-3</v>
+      </c>
+      <c r="M17" s="5">
+        <f t="shared" si="2"/>
+        <v>-1.1745211678817941E-2</v>
+      </c>
+      <c r="O17">
+        <v>-3.9419277329213298E-2</v>
+      </c>
+      <c r="P17">
+        <v>-0.109448577433232</v>
+      </c>
+      <c r="Q17" s="5">
+        <f t="shared" si="3"/>
+        <v>7.0029300104018699E-2</v>
+      </c>
+      <c r="S17">
+        <v>7.60708969489272E-2</v>
+      </c>
+      <c r="T17">
+        <v>9.8444559205724896E-2</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.2373662256797697E-2</v>
+      </c>
+      <c r="W17">
+        <v>0.16994915028806101</v>
+      </c>
+      <c r="X17">
+        <v>0.16994915028806101</v>
+      </c>
+      <c r="Y17" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>5.6846796386391197E-3</v>
+      </c>
+      <c r="AB17">
+        <v>5.6846796386391197E-3</v>
+      </c>
+      <c r="AC17" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5">
+        <f t="shared" si="7"/>
+        <v>7.0029300104018699E-2</v>
+      </c>
+      <c r="AF17" s="5">
+        <f t="shared" si="8"/>
+        <v>-3.4118873935615635E-2</v>
+      </c>
+      <c r="AG17" s="5">
+        <f>E17+I17</f>
+        <v>0.34286665208237566</v>
+      </c>
+      <c r="AI17" s="4">
+        <f>E17+I17+M17+Q17+U17+Y17+AC17</f>
+        <v>0.37877707825077872</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B16">
-        <v>0.14063965098947201</v>
-      </c>
-      <c r="C16">
+      <c r="C18" s="5">
         <v>-8.53676104400794E-2</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="D18" s="5">
+        <v>-0.36820494568268503</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.28283733524260563</v>
+      </c>
+      <c r="G18">
+        <v>7.2346729876637594E-2</v>
+      </c>
+      <c r="H18">
+        <v>1.7342576763045799E-2</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="1"/>
+        <v>5.5004153113591796E-2</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18">
+        <v>-1.2025895631619E-2</v>
+      </c>
+      <c r="L18">
+        <v>-6.1435498535575596E-3</v>
+      </c>
+      <c r="M18" s="5">
+        <f t="shared" si="2"/>
+        <v>-5.8823457780614406E-3</v>
+      </c>
+      <c r="O18">
+        <v>-0.134754265364598</v>
+      </c>
+      <c r="P18">
+        <v>-0.12831973946505601</v>
+      </c>
+      <c r="Q18" s="5">
+        <f t="shared" si="3"/>
+        <v>-6.4345258995419929E-3</v>
+      </c>
+      <c r="S18">
+        <v>0.124508999772188</v>
+      </c>
+      <c r="T18">
+        <v>0.147039681283958</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.2530681511769998E-2</v>
+      </c>
+      <c r="W18">
+        <v>0.115959358088856</v>
+      </c>
+      <c r="X18">
+        <v>0.15178952664165299</v>
+      </c>
+      <c r="Y18" s="5">
+        <f t="shared" si="5"/>
+        <v>-3.5830168552796984E-2</v>
+      </c>
+      <c r="AA18">
+        <v>-7.1113242576673098E-3</v>
+      </c>
+      <c r="AB18">
+        <v>1.03148126659045E-2</v>
+      </c>
+      <c r="AC18" s="5">
+        <f t="shared" si="6"/>
+        <v>-1.7426136923571811E-2</v>
+      </c>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5">
+        <f t="shared" si="7"/>
+        <v>-6.4345258995419929E-3</v>
+      </c>
+      <c r="AF18" s="5">
+        <f t="shared" si="8"/>
+        <v>-8.1669332766200239E-2</v>
+      </c>
+      <c r="AG18" s="5">
+        <f>E18+I18</f>
+        <v>0.33784148835619743</v>
+      </c>
+      <c r="AI18" s="4">
+        <f>E18+I18+M18+Q18+U18+Y18+AC18</f>
+        <v>0.24973762969045521</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>3</v>
       </c>
-      <c r="B17">
-        <v>2.87695140232813E-2</v>
-      </c>
-      <c r="C17">
+      <c r="C19" s="5">
         <v>-0.194568075207978</v>
       </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="D19" s="5">
+        <v>-0.59741121178864398</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.40284313658066595</v>
+      </c>
+      <c r="G19">
+        <v>7.9777253147179095E-2</v>
+      </c>
+      <c r="H19">
+        <v>3.03083378270185E-2</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="1"/>
+        <v>4.9468915320160595E-2</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19">
+        <v>-1.14904795380124E-2</v>
+      </c>
+      <c r="L19">
+        <v>-5.6932828844747001E-3</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="2"/>
+        <v>-5.7971966535376998E-3</v>
+      </c>
+      <c r="O19">
+        <v>-6.4067477393471503E-2</v>
+      </c>
+      <c r="P19">
+        <v>-5.5391695306414503E-2</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="3"/>
+        <v>-8.6757820870570004E-3</v>
+      </c>
+      <c r="S19">
+        <v>0.118033903265312</v>
+      </c>
+      <c r="T19">
+        <v>0.14017335810440201</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.2139454839090009E-2</v>
+      </c>
+      <c r="W19">
+        <v>0.107258849208799</v>
+      </c>
+      <c r="X19">
+        <v>0.14297809365901801</v>
+      </c>
+      <c r="Y19" s="5">
+        <f t="shared" si="5"/>
+        <v>-3.5719244450219012E-2</v>
+      </c>
+      <c r="AA19">
+        <v>-3.9361823659811801E-3</v>
+      </c>
+      <c r="AB19">
+        <v>1.3428687091220101E-2</v>
+      </c>
+      <c r="AC19" s="5">
+        <f t="shared" si="6"/>
+        <v>-1.7364869457201282E-2</v>
+      </c>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5">
+        <f t="shared" si="7"/>
+        <v>-8.6757820870570004E-3</v>
+      </c>
+      <c r="AF19" s="5">
+        <f t="shared" si="8"/>
+        <v>-8.1020765400048003E-2</v>
+      </c>
+      <c r="AG19" s="5">
+        <f>E19+I19</f>
+        <v>0.45231205190082657</v>
+      </c>
+      <c r="AI19" s="4">
+        <f>E19+I19+M19+Q19+U19+Y19+AC19</f>
+        <v>0.36261550441372159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B18">
-        <v>0.18881224837854199</v>
-      </c>
-      <c r="C18">
+      <c r="C20" s="5">
         <v>-2.9836760326829598E-2</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D20" s="5">
+        <v>-0.42474114525569501</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>0.39490438492886543</v>
+      </c>
+      <c r="G20">
+        <v>8.8515383497522901E-2</v>
+      </c>
+      <c r="H20">
+        <v>4.0534927781801303E-2</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="1"/>
+        <v>4.7980455715721598E-2</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20">
+        <v>-9.5126456296744898E-3</v>
+      </c>
+      <c r="L20">
+        <v>-5.2365158411973901E-3</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" si="2"/>
+        <v>-4.2761297884770996E-3</v>
+      </c>
+      <c r="O20">
+        <v>-0.110727166879507</v>
+      </c>
+      <c r="P20">
+        <v>-0.10225670887527</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="3"/>
+        <v>-8.4704580042369998E-3</v>
+      </c>
+      <c r="S20">
+        <v>0.12270904877794001</v>
+      </c>
+      <c r="T20">
+        <v>0.14433533645716301</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" si="4"/>
+        <v>-2.1626287679223005E-2</v>
+      </c>
+      <c r="W20">
+        <v>8.9169655673979206E-2</v>
+      </c>
+      <c r="X20">
+        <v>0.12461745241312799</v>
+      </c>
+      <c r="Y20" s="5">
+        <f t="shared" si="5"/>
+        <v>-3.5447796739148787E-2</v>
+      </c>
+      <c r="AA20">
+        <v>1.32367143557229E-3</v>
+      </c>
+      <c r="AB20">
+        <v>1.8546012422012599E-2</v>
+      </c>
+      <c r="AC20" s="5">
+        <f t="shared" si="6"/>
+        <v>-1.7222340986440311E-2</v>
+      </c>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5">
+        <f t="shared" si="7"/>
+        <v>-8.4704580042369998E-3</v>
+      </c>
+      <c r="AF20" s="5">
+        <f t="shared" si="8"/>
+        <v>-7.8572555193289206E-2</v>
+      </c>
+      <c r="AG20" s="5">
+        <f>E20+I20</f>
+        <v>0.442884840644587</v>
+      </c>
+      <c r="AI20" s="4">
+        <f>E20+I20+M20+Q20+U20+Y20+AC20</f>
+        <v>0.35584182744706078</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W1:Y1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="S2:U2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>